--- a/九龙-何文田-明寓/明寓_销控明细表.xlsx
+++ b/九龙-何文田-明寓/明寓_销控明细表.xlsx
@@ -755,7 +755,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2019-09-08</t>
+          <t>2019-09-09</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -821,7 +821,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2019-02-13</t>
+          <t>2019-02-14</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -887,7 +887,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -953,7 +953,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2019-09-25</t>
+          <t>2019-09-26</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2019-05-13</t>
+          <t>2019-05-14</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2019-05-07</t>
+          <t>2019-05-08</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2020-01-07</t>
+          <t>2020-01-08</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2019-04-01</t>
+          <t>2019-04-02</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2019-03-06</t>
+          <t>2019-03-07</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2019-03-24</t>
+          <t>2019-03-25</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2018-04-19</t>
+          <t>2018-04-20</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2018-11-05</t>
+          <t>2018-11-06</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2018-11-04</t>
+          <t>2018-11-05</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2021-07-05</t>
+          <t>2021-07-06</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2018-11-04</t>
+          <t>2018-11-05</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2018-11-04</t>
+          <t>2018-11-05</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -2038,7 +2038,7 @@
           <t>A | 2722呎 (4+房)
 $14800万
 $54,372/呎
-(19年-02月-13日)</t>
+(19年-02月-14日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -2046,7 +2046,7 @@
           <t>B | 2719呎 (4+房)
 $12800万
 $47,076/呎
-(19年-09月-08日)</t>
+(19年-09月-09日)</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2061,7 @@
           <t>A | 2722呎 (4+房)
 $8500万
 $31,227/呎
-(24年-11月-28日)</t>
+(24年-11月-29日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -2069,7 +2069,7 @@
           <t>B | 2718呎 (4+房)
 $8000万
 $29,433/呎
-(26年-07月-16日)</t>
+(26年-07月-17日)</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
           <t>B | 2719呎 (4+房)
 $10880万
 $40,015/呎
-(19年-09月-25日)</t>
+(19年-09月-26日)</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
           <t>A | 1310呎 (3房)
 $5109万
 $39,000/呎
-(19年-05月-07日)</t>
+(19年-05月-08日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -2115,7 +2115,7 @@
           <t>B | 1306呎 (3房)
 $5086万
 $38,940/呎
-(19年-05月-13日)</t>
+(19年-05月-14日)</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
           <t>A | 1310呎 (2房)
 $4821万
 $36,800/呎
-(19年-04月-01日)</t>
+(19年-04月-02日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -2138,7 +2138,7 @@
           <t>B | 1306呎 (3房)
 $4200万
 $32,159/呎
-(20年-01月-07日)</t>
+(20年-01月-08日)</t>
         </is>
       </c>
     </row>
@@ -2153,7 +2153,7 @@
           <t>A | 1310呎 (3房)
 $4297万
 $32,802/呎
-(19年-03月-24日)</t>
+(19年-03月-25日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -2161,7 +2161,7 @@
           <t>B | 1306呎 (3房)
 $4499万
 $34,447/呎
-(19年-03月-06日)</t>
+(19年-03月-07日)</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
           <t>A | 1310呎 (3房)
 $4061万
 $31,000/呎
-(18年-11月-05日)</t>
+(18年-11月-06日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -2184,7 +2184,7 @@
           <t>B | 1306呎 (3房)
 $4808万
 $36,815/呎
-(18年-04月-19日)</t>
+(18年-04月-20日)</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
           <t>A | 1310呎 (3房)
 $4100万
 $31,298/呎
-(21年-07月-05日)</t>
+(21年-07月-06日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -2207,7 +2207,7 @@
           <t>B | 1306呎 (3房)
 $3736万
 $28,606/呎
-(18年-11月-04日)</t>
+(18年-11月-05日)</t>
         </is>
       </c>
     </row>
@@ -2222,7 +2222,7 @@
           <t>A | 1310呎 (3房)
 $3541万
 $27,029/呎
-(18年-11月-04日)</t>
+(18年-11月-05日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -2230,7 +2230,7 @@
           <t>B | 1306呎 (3房)
 $3694万
 $28,281/呎
-(18年-11月-04日)</t>
+(18年-11月-05日)</t>
         </is>
       </c>
     </row>

--- a/九龙-何文田-明寓/明寓_销控明细表.xlsx
+++ b/九龙-何文田-明寓/明寓_销控明细表.xlsx
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>2718</v>
+        <v>2719</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -887,14 +887,14 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
         <v>80000000</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>29433</v>
+        <v>29423</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -2066,10 +2066,10 @@
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>B | 2718呎 (4+房)
+          <t>B | 2719呎 (4+房)
 $8000万
-$29,433/呎
-(26年-07月-17日)</t>
+$29,423/呎
+(26年-08月-03日)</t>
         </is>
       </c>
     </row>
